--- a/output/pdf_financials_xlsx/KITS.xlsx
+++ b/output/pdf_financials_xlsx/KITS.xlsx
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.693</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>1.452</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.356</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">

--- a/output/pdf_financials_xlsx/KITS.xlsx
+++ b/output/pdf_financials_xlsx/KITS.xlsx
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>4.179</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>4.732</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>5.173</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>8.956</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>8.608000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -1688,19 +1688,19 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>0.756</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>1.904</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>4.478</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="58">
@@ -3110,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.213</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -5733,7 +5733,11 @@
           <t>Repurchase of shares (Note 19)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -6129,7 +6133,11 @@
           <t>Net Income (Loss) $</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>-14.617</v>
       </c>
@@ -6431,7 +6439,11 @@
           <t>Net Income / (Loss) $</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
